--- a/documentacion/plan-requisitos.xlsx
+++ b/documentacion/plan-requisitos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0f06017abd79a982/Escritorio/ingenieria-software-2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MI PC\Handgelus\documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_A7D544611E6D2DB50E3DB31853A23C2824BD46F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16F74EBF-3DF4-4B86-9BBD-B502FC8DFE24}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C754EB59-6AF7-43DD-AA4E-55C7AB9587E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,9 +107,6 @@
     <t>Como administrador del sistema, necesito crear y administrar las cuentas de la asistente, el tatuador/artista y otros administradores, asignando un rol a cada una, para controlar quién puede acceder a cada módulo del sistema.</t>
   </si>
   <si>
-    <t>El sistema debe permitir crear, consultar y actualizar cuentas de usuario con un rol asociado (cliente, asistente, tatuador/artista, administrador), autenticar a los usuarios mediante credenciales únicas, restringir el acceso a las funcionalidades según el rol autenticado y proteger las credenciales mediante cifrado.</t>
-  </si>
-  <si>
     <t>SWR-01 — El sistema debe permitir al administrador crear cuentas de asistente, tatuador/artista y administrador, asignando un rol único a cada cuenta.</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>Como propietario del negocio, necesito definir y actualizar los valores base de la tabla de tarifas por tamaño y tipo de servicio, para que el sistema calcule cotizaciones preliminares coherentes con mis precios actuales.</t>
   </si>
   <si>
-    <t>El sistema debe permitir al propietario registrar, consultar y modificar los valores base de la tabla de tarifas utilizada por la calculadora de cotizaciones, garantizando que los cambios futuros no alteren cotizaciones ya generadas.</t>
-  </si>
-  <si>
     <t>SWR-04 — El sistema debe permitir al propietario registrar y actualizar los valores base de la tabla de tarifas por tamaño y tipo de servicio (tatuaje o comisión).</t>
   </si>
   <si>
@@ -185,9 +179,6 @@
     <t>Como cliente, necesito enviar mi solicitud de servicio (tatuaje o comisión) desde una interfaz en línea, indicando tipo de servicio, tamaño, zona/destino y referencias, sin depender de canales informales.</t>
   </si>
   <si>
-    <t>El sistema debe permitir a los clientes registrar solicitudes de servicio de tatuaje o de obra por comisión mediante un formulario web, validar los datos obligatorios y almacenar la solicitud con estado inicial 'Recibida'.</t>
-  </si>
-  <si>
     <t>SWR-06 — El sistema debe validar que el cliente esté registrado (nombre, correo único, teléfono) antes de aceptar una solicitud.</t>
   </si>
   <si>
@@ -221,9 +212,6 @@
     <t>Como tatuador/artista, necesito revisar y ajustar la cotización generada automáticamente antes de confirmarla al cliente, para asegurar que el valor final sea correcto.</t>
   </si>
   <si>
-    <t>El sistema debe calcular una cotización preliminar basada en la tabla de tarifas configurable (F-02), permitir su ajuste por el tatuador/artista, notificar al cliente y registrar su decisión de aceptación o rechazo.</t>
-  </si>
-  <si>
     <t>SWR-09 — El sistema debe calcular automáticamente una cotización preliminar según tamaño y tipo de servicio, usando la tabla de tarifas vigente.</t>
   </si>
   <si>
@@ -263,9 +251,6 @@
     <t>Como asistente, necesito que el sistema registre y verifique automáticamente los pagos parciales realizados por el cliente, para no depender de la verificación manual.</t>
   </si>
   <si>
-    <t>El sistema debe registrar el pago del abono o anticipo integrado con la pasarela de pago externa, verificar automáticamente su confirmación y actualizar el estado del servicio en consecuencia.</t>
-  </si>
-  <si>
     <t>SWR-12 — El sistema debe registrar el pago de abono (mínimo 30% para tatuaje) o anticipo (50% para comisión) mediante la pasarela de pago.</t>
   </si>
   <si>
@@ -299,9 +284,6 @@
     <t>Como asistente, necesito agendar citas de tatuaje verificando la disponibilidad real del tatuador, para evitar conflictos de horario.</t>
   </si>
   <si>
-    <t>El sistema debe permitir agendar una cita de tatuaje según la disponibilidad del tatuador, bloquear la jornada seleccionada y generar un comprobante de confirmación para el cliente.</t>
-  </si>
-  <si>
     <t>SWR-15 — El sistema debe impedir agendar una cita en una jornada ya ocupada, permitiendo máximo 2 citas por día.</t>
   </si>
   <si>
@@ -335,9 +317,6 @@
     <t>Como cliente, necesito consultar en tiempo real el estado de mi obra por comisión, para conocer el avance sin tener que preguntar directamente al artista.</t>
   </si>
   <si>
-    <t>El sistema debe permitir al artista actualizar el estado de avance de una obra por comisión y al cliente consultar dicho estado en tiempo real, restringiendo el acceso solo a sus propias comisiones.</t>
-  </si>
-  <si>
     <t>SWR-18 — El sistema debe permitir al artista actualizar el estado de una obra entre: en espera, en producción, terminada, enviada.</t>
   </si>
   <si>
@@ -366,9 +345,6 @@
   </si>
   <si>
     <t>Como asistente, necesito consultar el historial completo de servicios de un cliente, para atenderlo con contexto sin depender de la memoria o de conversaciones anteriores.</t>
-  </si>
-  <si>
-    <t>El sistema debe generar un historial de servicios por cliente, incluyendo tipo de servicio, fecha, valor, estado y comprobantes, consultable por la asistente y el propietario.</t>
   </si>
   <si>
     <t>SWR-21 — El sistema debe generar el historial de servicios de cada cliente con tipo de servicio, fecha, valor, estado y comprobantes asociados.</t>
@@ -576,6 +552,30 @@
   </si>
   <si>
     <t>Generar cotización</t>
+  </si>
+  <si>
+    <t>El software debe permitir crear, consultar y actualizar cuentas de usuario con un rol asociado (cliente, asistente, tatuador/artista, administrador), autenticar a los usuarios mediante credenciales únicas, restringir el acceso a las funcionalidades según el rol autenticado y proteger las credenciales mediante cifrado.</t>
+  </si>
+  <si>
+    <t>El software debe permitir al propietario registrar, consultar y modificar los valores base de la tabla de tarifas utilizada por la calculadora de cotizaciones, garantizando que los cambios futuros no alteren cotizaciones ya generadas.</t>
+  </si>
+  <si>
+    <t>El software debe permitir al artista actualizar el estado de avance de una obra por comisión y al cliente consultar dicho estado en tiempo real, restringiendo el acceso solo a sus propias comisiones.</t>
+  </si>
+  <si>
+    <t>El software debe permitir agendar una cita de tatuaje según la disponibilidad del tatuador, bloquear la jornada seleccionada y generar un comprobante de confirmación para el cliente.</t>
+  </si>
+  <si>
+    <t>El software debe registrar el pago del abono o anticipo integrado con la pasarela de pago externa, verificar automáticamente su confirmación y actualizar el estado del servicio en consecuencia.</t>
+  </si>
+  <si>
+    <t>El software debe permitir a los clientes registrar solicitudes de servicio de tatuaje o de obra por comisión mediante un formulario web, validar los datos obligatorios y almacenar la solicitud con estado inicial 'Recibida'.</t>
+  </si>
+  <si>
+    <t>El software debe generar un historial de servicios por cliente, incluyendo tipo de servicio, fecha, valor, estado y comprobantes, consultable por la asistente y el propietario.</t>
+  </si>
+  <si>
+    <t>El software debe calcular una cotización preliminar basada en la tabla de tarifas configurable (F-02), permitir su ajuste por el tatuador/artista, notificar al cliente y registrar su decisión de aceptación o rechazo.</t>
   </si>
 </sst>
 </file>
@@ -922,28 +922,9 @@
     <xf numFmtId="164" fontId="8" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -961,6 +942,25 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1249,7 +1249,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="38"/>
@@ -1284,7 +1284,7 @@
       <c r="AE1" s="1"/>
     </row>
     <row r="2" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="38"/>
@@ -1346,10 +1346,10 @@
       <c r="I3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="J3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="43"/>
+      <c r="K3" s="36"/>
       <c r="L3" s="26" t="s">
         <v>12</v>
       </c>
@@ -1396,70 +1396,70 @@
       <c r="AE3" s="7"/>
     </row>
     <row r="4" spans="1:31" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="G4" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="H4" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="34" t="s">
+      <c r="K4" s="39"/>
+      <c r="L4" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K4" s="35"/>
-      <c r="L4" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M4" s="19">
         <v>3</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O4" s="19">
         <v>3</v>
       </c>
       <c r="P4" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="R4" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="T4" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R4" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="T4" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" s="19" t="s">
+      <c r="V4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V4" s="19" t="s">
+      <c r="W4" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W4" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
@@ -1471,56 +1471,56 @@
       <c r="AE4" s="11"/>
     </row>
     <row r="5" spans="1:31" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
       <c r="F5" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="27" t="s">
-        <v>37</v>
-      </c>
       <c r="H5" s="19" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="I5" s="19"/>
-      <c r="J5" s="34" t="s">
+      <c r="J5" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="39"/>
+      <c r="L5" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K5" s="35"/>
-      <c r="L5" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M5" s="19">
         <v>3</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O5" s="19">
         <v>3</v>
       </c>
       <c r="P5" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="R5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" s="39"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="19" t="s">
+      <c r="V5" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V5" s="19" t="s">
+      <c r="W5" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W5" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
@@ -1532,56 +1532,56 @@
       <c r="AE5" s="11"/>
     </row>
     <row r="6" spans="1:31" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
+      <c r="A6" s="41"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
       <c r="F6" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="27" t="s">
-        <v>39</v>
-      </c>
       <c r="H6" s="19" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I6" s="19"/>
-      <c r="J6" s="34" t="s">
+      <c r="J6" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="39"/>
+      <c r="L6" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K6" s="35"/>
-      <c r="L6" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M6" s="19">
         <v>2</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O6" s="19">
         <v>2</v>
       </c>
       <c r="P6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="R6" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" s="39"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R6" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="19" t="s">
+      <c r="V6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V6" s="19" t="s">
+      <c r="W6" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W6" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
@@ -1593,70 +1593,70 @@
       <c r="AE6" s="11"/>
     </row>
     <row r="7" spans="1:31" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="C7" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="D7" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="E7" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="G7" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>46</v>
-      </c>
       <c r="H7" s="19" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="I7" s="19"/>
-      <c r="J7" s="34" t="s">
+      <c r="J7" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="39"/>
+      <c r="L7" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K7" s="35"/>
-      <c r="L7" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M7" s="19">
         <v>2</v>
       </c>
       <c r="N7" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O7" s="19">
         <v>2</v>
       </c>
       <c r="P7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q7" s="19" t="s">
+      <c r="R7" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S7" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="T7" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="U7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R7" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S7" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="T7" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="U7" s="19" t="s">
+      <c r="V7" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V7" s="19" t="s">
+      <c r="W7" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W7" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
@@ -1668,56 +1668,56 @@
       <c r="AE7" s="11"/>
     </row>
     <row r="8" spans="1:31" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
+      <c r="A8" s="41"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
       <c r="F8" s="27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I8" s="19"/>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="L8" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K8" s="35"/>
-      <c r="L8" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M8" s="19">
         <v>2</v>
       </c>
       <c r="N8" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O8" s="19">
         <v>2</v>
       </c>
       <c r="P8" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q8" s="19" t="s">
+      <c r="R8" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" s="39"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R8" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="19" t="s">
+      <c r="V8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V8" s="19" t="s">
+      <c r="W8" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W8" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
@@ -1729,70 +1729,70 @@
       <c r="AE8" s="11"/>
     </row>
     <row r="9" spans="1:31" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="D9" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="E9" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="G9" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="H9" s="19" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="I9" s="19"/>
-      <c r="J9" s="34" t="s">
+      <c r="J9" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="39"/>
+      <c r="L9" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K9" s="35"/>
-      <c r="L9" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M9" s="19">
         <v>2</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O9" s="19">
         <v>1</v>
       </c>
       <c r="P9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="R9" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="T9" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="U9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R9" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="T9" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="U9" s="19" t="s">
+      <c r="V9" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V9" s="19" t="s">
+      <c r="W9" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W9" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
@@ -1804,56 +1804,56 @@
       <c r="AE9" s="11"/>
     </row>
     <row r="10" spans="1:31" ht="82.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
       <c r="F10" s="27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I10" s="19"/>
-      <c r="J10" s="34" t="s">
+      <c r="J10" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="39"/>
+      <c r="L10" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K10" s="35"/>
-      <c r="L10" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M10" s="19">
         <v>3</v>
       </c>
       <c r="N10" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O10" s="19">
         <v>2</v>
       </c>
       <c r="P10" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q10" s="19" t="s">
+      <c r="R10" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" s="39"/>
+      <c r="T10" s="39"/>
+      <c r="U10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R10" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="19" t="s">
+      <c r="V10" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V10" s="19" t="s">
+      <c r="W10" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W10" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
@@ -1865,56 +1865,56 @@
       <c r="AE10" s="11"/>
     </row>
     <row r="11" spans="1:31" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
       <c r="F11" s="27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I11" s="19"/>
-      <c r="J11" s="34" t="s">
+      <c r="J11" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="39"/>
+      <c r="L11" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K11" s="35"/>
-      <c r="L11" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M11" s="19">
         <v>3</v>
       </c>
       <c r="N11" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O11" s="19">
         <v>3</v>
       </c>
       <c r="P11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q11" s="19" t="s">
+      <c r="R11" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S11" s="39"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R11" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="19" t="s">
+      <c r="V11" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V11" s="19" t="s">
+      <c r="W11" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W11" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X11" s="11"/>
       <c r="Y11" s="11"/>
@@ -1926,70 +1926,70 @@
       <c r="AE11" s="11"/>
     </row>
     <row r="12" spans="1:31" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="36" t="s">
+      <c r="G12" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="H12" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>69</v>
-      </c>
       <c r="I12" s="19"/>
-      <c r="J12" s="34" t="s">
+      <c r="J12" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="39"/>
+      <c r="L12" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K12" s="35"/>
-      <c r="L12" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M12" s="19">
         <v>4</v>
       </c>
       <c r="N12" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O12" s="19">
         <v>3</v>
       </c>
       <c r="P12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q12" s="19" t="s">
+      <c r="R12" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="T12" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="U12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S12" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="T12" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="U12" s="19" t="s">
+      <c r="V12" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V12" s="19" t="s">
+      <c r="W12" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W12" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
@@ -2001,56 +2001,56 @@
       <c r="AE12" s="11"/>
     </row>
     <row r="13" spans="1:31" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
       <c r="F13" s="27" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I13" s="19"/>
-      <c r="J13" s="34" t="s">
+      <c r="J13" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="39"/>
+      <c r="L13" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K13" s="35"/>
-      <c r="L13" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M13" s="19">
         <v>3</v>
       </c>
       <c r="N13" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O13" s="19">
         <v>2</v>
       </c>
       <c r="P13" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q13" s="19" t="s">
+      <c r="R13" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R13" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="19" t="s">
+      <c r="V13" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V13" s="19" t="s">
+      <c r="W13" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W13" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
@@ -2062,56 +2062,56 @@
       <c r="AE13" s="11"/>
     </row>
     <row r="14" spans="1:31" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I14" s="19"/>
-      <c r="J14" s="34" t="s">
+      <c r="J14" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="39"/>
+      <c r="L14" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K14" s="35"/>
-      <c r="L14" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M14" s="19">
         <v>3</v>
       </c>
       <c r="N14" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O14" s="19">
         <v>3</v>
       </c>
       <c r="P14" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q14" s="19" t="s">
+      <c r="R14" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R14" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="19" t="s">
+      <c r="V14" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V14" s="19" t="s">
+      <c r="W14" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W14" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
@@ -2123,70 +2123,70 @@
       <c r="AE14" s="11"/>
     </row>
     <row r="15" spans="1:31" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="G15" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>82</v>
-      </c>
       <c r="H15" s="19" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I15" s="19"/>
-      <c r="J15" s="34" t="s">
+      <c r="J15" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="39"/>
+      <c r="L15" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K15" s="35"/>
-      <c r="L15" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M15" s="19">
         <v>4</v>
       </c>
       <c r="N15" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O15" s="19">
         <v>4</v>
       </c>
       <c r="P15" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q15" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q15" s="19" t="s">
+      <c r="R15" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="T15" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="U15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R15" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S15" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="T15" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="U15" s="19" t="s">
+      <c r="V15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V15" s="19" t="s">
+      <c r="W15" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W15" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
@@ -2198,56 +2198,56 @@
       <c r="AE15" s="11"/>
     </row>
     <row r="16" spans="1:31" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
       <c r="F16" s="19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I16" s="19"/>
-      <c r="J16" s="34" t="s">
+      <c r="J16" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" s="39"/>
+      <c r="L16" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K16" s="35"/>
-      <c r="L16" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M16" s="19">
         <v>3</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O16" s="19">
         <v>3</v>
       </c>
       <c r="P16" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q16" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q16" s="19" t="s">
+      <c r="R16" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R16" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="19" t="s">
+      <c r="V16" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V16" s="19" t="s">
+      <c r="W16" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W16" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
@@ -2259,56 +2259,56 @@
       <c r="AE16" s="11"/>
     </row>
     <row r="17" spans="1:31" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
+      <c r="A17" s="41"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
       <c r="F17" s="19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I17" s="19"/>
-      <c r="J17" s="34" t="s">
+      <c r="J17" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="39"/>
+      <c r="L17" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K17" s="35"/>
-      <c r="L17" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M17" s="19">
         <v>2</v>
       </c>
       <c r="N17" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O17" s="19">
         <v>2</v>
       </c>
       <c r="P17" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q17" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q17" s="19" t="s">
+      <c r="R17" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R17" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="19" t="s">
+      <c r="V17" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V17" s="19" t="s">
+      <c r="W17" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W17" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
@@ -2320,70 +2320,70 @@
       <c r="AE17" s="11"/>
     </row>
     <row r="18" spans="1:31" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="H18" s="19" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I18" s="19"/>
-      <c r="J18" s="34" t="s">
+      <c r="J18" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="39"/>
+      <c r="L18" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K18" s="35"/>
-      <c r="L18" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M18" s="19">
         <v>3</v>
       </c>
       <c r="N18" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O18" s="19">
         <v>3</v>
       </c>
       <c r="P18" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q18" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q18" s="19" t="s">
+      <c r="R18" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S18" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="T18" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="U18" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R18" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S18" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="T18" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="U18" s="19" t="s">
+      <c r="V18" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V18" s="19" t="s">
+      <c r="W18" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W18" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
@@ -2395,56 +2395,56 @@
       <c r="AE18" s="11"/>
     </row>
     <row r="19" spans="1:31" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
       <c r="F19" s="19" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="34" t="s">
+      <c r="J19" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="39"/>
+      <c r="L19" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K19" s="35"/>
-      <c r="L19" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M19" s="19">
         <v>2</v>
       </c>
       <c r="N19" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19" s="19">
         <v>2</v>
       </c>
       <c r="P19" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q19" s="19" t="s">
+      <c r="R19" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S19" s="39"/>
+      <c r="T19" s="39"/>
+      <c r="U19" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R19" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="19" t="s">
+      <c r="V19" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V19" s="19" t="s">
+      <c r="W19" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W19" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
@@ -2456,56 +2456,56 @@
       <c r="AE19" s="11"/>
     </row>
     <row r="20" spans="1:31" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
+      <c r="A20" s="41"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
       <c r="F20" s="19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I20" s="19"/>
-      <c r="J20" s="34" t="s">
+      <c r="J20" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="39"/>
+      <c r="L20" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="K20" s="35"/>
-      <c r="L20" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="M20" s="19">
         <v>2</v>
       </c>
       <c r="N20" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O20" s="19">
         <v>1</v>
       </c>
       <c r="P20" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q20" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q20" s="19" t="s">
+      <c r="R20" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S20" s="39"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R20" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="19" t="s">
+      <c r="V20" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V20" s="19" t="s">
+      <c r="W20" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W20" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
@@ -2517,70 +2517,70 @@
       <c r="AE20" s="11"/>
     </row>
     <row r="21" spans="1:31" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>104</v>
+      <c r="A21" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>161</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I21" s="19"/>
-      <c r="J21" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="35"/>
+      <c r="J21" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="39"/>
       <c r="L21" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M21" s="19">
         <v>2</v>
       </c>
       <c r="N21" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O21" s="19">
         <v>2</v>
       </c>
       <c r="P21" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q21" s="19" t="s">
+      <c r="R21" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S21" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="T21" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="U21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R21" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S21" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="T21" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="U21" s="19" t="s">
+      <c r="V21" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V21" s="19" t="s">
+      <c r="W21" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W21" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
@@ -2592,56 +2592,56 @@
       <c r="AE21" s="11"/>
     </row>
     <row r="22" spans="1:31" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
       <c r="F22" s="19" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K22" s="35"/>
+      <c r="J22" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="39"/>
       <c r="L22" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M22" s="19">
         <v>2</v>
       </c>
       <c r="N22" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O22" s="19">
         <v>2</v>
       </c>
       <c r="P22" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q22" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q22" s="19" t="s">
+      <c r="R22" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S22" s="31"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R22" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S22" s="34"/>
-      <c r="T22" s="40"/>
-      <c r="U22" s="19" t="s">
+      <c r="V22" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V22" s="19" t="s">
+      <c r="W22" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W22" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
@@ -2653,56 +2653,56 @@
       <c r="AE22" s="11"/>
     </row>
     <row r="23" spans="1:31" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
       <c r="F23" s="19" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I23" s="19"/>
-      <c r="J23" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K23" s="35"/>
+      <c r="J23" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="39"/>
       <c r="L23" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M23" s="19">
         <v>3</v>
       </c>
       <c r="N23" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O23" s="19">
         <v>3</v>
       </c>
       <c r="P23" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q23" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q23" s="19" t="s">
+      <c r="R23" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S23" s="31"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R23" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S23" s="34"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="19" t="s">
+      <c r="V23" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V23" s="19" t="s">
+      <c r="W23" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W23" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
@@ -2715,69 +2715,69 @@
     </row>
     <row r="24" spans="1:31" ht="196.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I24" s="19"/>
-      <c r="J24" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24" s="35"/>
+      <c r="J24" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="39"/>
       <c r="L24" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M24" s="19">
         <v>2</v>
       </c>
       <c r="N24" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O24" s="19">
         <v>2</v>
       </c>
       <c r="P24" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q24" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q24" s="19" t="s">
+      <c r="R24" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S24" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="U24" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="R24" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="S24" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="T24" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="U24" s="19" t="s">
+      <c r="V24" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V24" s="19" t="s">
+      <c r="W24" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="W24" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
@@ -2798,8 +2798,8 @@
       <c r="G25" s="28"/>
       <c r="H25" s="28"/>
       <c r="I25" s="28"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="32"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="44"/>
       <c r="L25" s="28"/>
       <c r="M25" s="28"/>
       <c r="N25" s="28"/>
@@ -2831,8 +2831,8 @@
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="I26" s="28"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="32"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="44"/>
       <c r="L26" s="28"/>
       <c r="M26" s="28"/>
       <c r="N26" s="28"/>
@@ -2864,8 +2864,8 @@
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
       <c r="I27" s="28"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="32"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="44"/>
       <c r="L27" s="28"/>
       <c r="M27" s="28"/>
       <c r="N27" s="28"/>
@@ -2897,8 +2897,8 @@
       <c r="G28" s="29"/>
       <c r="H28" s="29"/>
       <c r="I28" s="29"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="32"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="44"/>
       <c r="L28" s="29"/>
       <c r="M28" s="29"/>
       <c r="N28" s="29"/>
@@ -2930,8 +2930,8 @@
       <c r="G29" s="29"/>
       <c r="H29" s="29"/>
       <c r="I29" s="29"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="32"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
       <c r="L29" s="29"/>
       <c r="M29" s="29"/>
       <c r="N29" s="29"/>
@@ -2963,8 +2963,8 @@
       <c r="G30" s="29"/>
       <c r="H30" s="29"/>
       <c r="I30" s="29"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="32"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="44"/>
       <c r="L30" s="29"/>
       <c r="M30" s="29"/>
       <c r="N30" s="29"/>
@@ -2996,8 +2996,8 @@
       <c r="G31" s="29"/>
       <c r="H31" s="29"/>
       <c r="I31" s="29"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="32"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="44"/>
       <c r="L31" s="29"/>
       <c r="M31" s="29"/>
       <c r="N31" s="29"/>
@@ -3029,8 +3029,8 @@
       <c r="G32" s="29"/>
       <c r="H32" s="29"/>
       <c r="I32" s="29"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="32"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="44"/>
       <c r="L32" s="29"/>
       <c r="M32" s="29"/>
       <c r="N32" s="29"/>
@@ -3062,8 +3062,8 @@
       <c r="G33" s="29"/>
       <c r="H33" s="29"/>
       <c r="I33" s="29"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="32"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="44"/>
       <c r="L33" s="29"/>
       <c r="M33" s="29"/>
       <c r="N33" s="29"/>
@@ -3095,8 +3095,8 @@
       <c r="G34" s="29"/>
       <c r="H34" s="29"/>
       <c r="I34" s="29"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="32"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="44"/>
       <c r="L34" s="29"/>
       <c r="M34" s="29"/>
       <c r="N34" s="29"/>
@@ -3128,8 +3128,8 @@
       <c r="G35" s="29"/>
       <c r="H35" s="29"/>
       <c r="I35" s="29"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="32"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="44"/>
       <c r="L35" s="29"/>
       <c r="M35" s="29"/>
       <c r="N35" s="29"/>
@@ -3161,8 +3161,8 @@
       <c r="G36" s="29"/>
       <c r="H36" s="29"/>
       <c r="I36" s="29"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="32"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="44"/>
       <c r="L36" s="29"/>
       <c r="M36" s="29"/>
       <c r="N36" s="29"/>
@@ -3194,8 +3194,8 @@
       <c r="G37" s="29"/>
       <c r="H37" s="29"/>
       <c r="I37" s="29"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="32"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="44"/>
       <c r="L37" s="29"/>
       <c r="M37" s="29"/>
       <c r="N37" s="29"/>
@@ -3227,8 +3227,8 @@
       <c r="G38" s="29"/>
       <c r="H38" s="29"/>
       <c r="I38" s="29"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="32"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="44"/>
       <c r="L38" s="29"/>
       <c r="M38" s="29"/>
       <c r="N38" s="29"/>
@@ -3260,8 +3260,8 @@
       <c r="G39" s="29"/>
       <c r="H39" s="29"/>
       <c r="I39" s="29"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="32"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="44"/>
       <c r="L39" s="29"/>
       <c r="M39" s="29"/>
       <c r="N39" s="29"/>
@@ -3293,8 +3293,8 @@
       <c r="G40" s="29"/>
       <c r="H40" s="29"/>
       <c r="I40" s="29"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="32"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="44"/>
       <c r="L40" s="29"/>
       <c r="M40" s="29"/>
       <c r="N40" s="29"/>
@@ -3326,8 +3326,8 @@
       <c r="G41" s="29"/>
       <c r="H41" s="29"/>
       <c r="I41" s="29"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="32"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="44"/>
       <c r="L41" s="29"/>
       <c r="M41" s="29"/>
       <c r="N41" s="29"/>
@@ -3359,8 +3359,8 @@
       <c r="G42" s="29"/>
       <c r="H42" s="29"/>
       <c r="I42" s="29"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="32"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="44"/>
       <c r="L42" s="29"/>
       <c r="M42" s="29"/>
       <c r="N42" s="29"/>
@@ -3392,8 +3392,8 @@
       <c r="G43" s="29"/>
       <c r="H43" s="29"/>
       <c r="I43" s="29"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="32"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="44"/>
       <c r="L43" s="29"/>
       <c r="M43" s="29"/>
       <c r="N43" s="29"/>
@@ -3425,8 +3425,8 @@
       <c r="G44" s="29"/>
       <c r="H44" s="29"/>
       <c r="I44" s="29"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="32"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="44"/>
       <c r="L44" s="29"/>
       <c r="M44" s="29"/>
       <c r="N44" s="29"/>
@@ -3458,8 +3458,8 @@
       <c r="G45" s="29"/>
       <c r="H45" s="29"/>
       <c r="I45" s="29"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="32"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="44"/>
       <c r="L45" s="29"/>
       <c r="M45" s="29"/>
       <c r="N45" s="29"/>
@@ -3491,8 +3491,8 @@
       <c r="G46" s="29"/>
       <c r="H46" s="29"/>
       <c r="I46" s="29"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="32"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="44"/>
       <c r="L46" s="29"/>
       <c r="M46" s="29"/>
       <c r="N46" s="29"/>
@@ -3524,8 +3524,8 @@
       <c r="G47" s="29"/>
       <c r="H47" s="29"/>
       <c r="I47" s="29"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="32"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="44"/>
       <c r="L47" s="29"/>
       <c r="M47" s="29"/>
       <c r="N47" s="29"/>
@@ -3557,8 +3557,8 @@
       <c r="G48" s="29"/>
       <c r="H48" s="29"/>
       <c r="I48" s="29"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="32"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="44"/>
       <c r="L48" s="29"/>
       <c r="M48" s="29"/>
       <c r="N48" s="29"/>
@@ -3590,8 +3590,8 @@
       <c r="G49" s="29"/>
       <c r="H49" s="29"/>
       <c r="I49" s="29"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="32"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="44"/>
       <c r="L49" s="29"/>
       <c r="M49" s="29"/>
       <c r="N49" s="29"/>
@@ -3623,8 +3623,8 @@
       <c r="G50" s="29"/>
       <c r="H50" s="29"/>
       <c r="I50" s="29"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="32"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="44"/>
       <c r="L50" s="29"/>
       <c r="M50" s="29"/>
       <c r="N50" s="29"/>
@@ -3656,8 +3656,8 @@
       <c r="G51" s="29"/>
       <c r="H51" s="29"/>
       <c r="I51" s="29"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="32"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="44"/>
       <c r="L51" s="29"/>
       <c r="M51" s="29"/>
       <c r="N51" s="29"/>
@@ -3689,8 +3689,8 @@
       <c r="G52" s="29"/>
       <c r="H52" s="29"/>
       <c r="I52" s="29"/>
-      <c r="J52" s="31"/>
-      <c r="K52" s="32"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="44"/>
       <c r="L52" s="29"/>
       <c r="M52" s="29"/>
       <c r="N52" s="29"/>
@@ -3722,8 +3722,8 @@
       <c r="G53" s="29"/>
       <c r="H53" s="29"/>
       <c r="I53" s="29"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="32"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="44"/>
       <c r="L53" s="29"/>
       <c r="M53" s="29"/>
       <c r="N53" s="29"/>
@@ -3755,8 +3755,8 @@
       <c r="G54" s="29"/>
       <c r="H54" s="29"/>
       <c r="I54" s="29"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="32"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="44"/>
       <c r="L54" s="29"/>
       <c r="M54" s="29"/>
       <c r="N54" s="29"/>
@@ -3788,8 +3788,8 @@
       <c r="G55" s="29"/>
       <c r="H55" s="29"/>
       <c r="I55" s="29"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="32"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="44"/>
       <c r="L55" s="29"/>
       <c r="M55" s="29"/>
       <c r="N55" s="29"/>
@@ -3821,8 +3821,8 @@
       <c r="G56" s="29"/>
       <c r="H56" s="29"/>
       <c r="I56" s="29"/>
-      <c r="J56" s="31"/>
-      <c r="K56" s="32"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="44"/>
       <c r="L56" s="29"/>
       <c r="M56" s="29"/>
       <c r="N56" s="29"/>
@@ -3854,8 +3854,8 @@
       <c r="G57" s="29"/>
       <c r="H57" s="29"/>
       <c r="I57" s="29"/>
-      <c r="J57" s="31"/>
-      <c r="K57" s="32"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="44"/>
       <c r="L57" s="29"/>
       <c r="M57" s="29"/>
       <c r="N57" s="29"/>
@@ -3887,8 +3887,8 @@
       <c r="G58" s="29"/>
       <c r="H58" s="29"/>
       <c r="I58" s="29"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="32"/>
+      <c r="J58" s="43"/>
+      <c r="K58" s="44"/>
       <c r="L58" s="29"/>
       <c r="M58" s="29"/>
       <c r="N58" s="29"/>
@@ -3920,8 +3920,8 @@
       <c r="G59" s="29"/>
       <c r="H59" s="29"/>
       <c r="I59" s="29"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="32"/>
+      <c r="J59" s="43"/>
+      <c r="K59" s="44"/>
       <c r="L59" s="29"/>
       <c r="M59" s="29"/>
       <c r="N59" s="29"/>
@@ -3953,8 +3953,8 @@
       <c r="G60" s="29"/>
       <c r="H60" s="29"/>
       <c r="I60" s="29"/>
-      <c r="J60" s="31"/>
-      <c r="K60" s="32"/>
+      <c r="J60" s="43"/>
+      <c r="K60" s="44"/>
       <c r="L60" s="29"/>
       <c r="M60" s="29"/>
       <c r="N60" s="29"/>
@@ -3986,8 +3986,8 @@
       <c r="G61" s="29"/>
       <c r="H61" s="29"/>
       <c r="I61" s="29"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="32"/>
+      <c r="J61" s="43"/>
+      <c r="K61" s="44"/>
       <c r="L61" s="29"/>
       <c r="M61" s="29"/>
       <c r="N61" s="29"/>
@@ -4019,8 +4019,8 @@
       <c r="G62" s="29"/>
       <c r="H62" s="29"/>
       <c r="I62" s="29"/>
-      <c r="J62" s="31"/>
-      <c r="K62" s="32"/>
+      <c r="J62" s="43"/>
+      <c r="K62" s="44"/>
       <c r="L62" s="29"/>
       <c r="M62" s="29"/>
       <c r="N62" s="29"/>
@@ -4052,8 +4052,8 @@
       <c r="G63" s="29"/>
       <c r="H63" s="29"/>
       <c r="I63" s="29"/>
-      <c r="J63" s="31"/>
-      <c r="K63" s="32"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="44"/>
       <c r="L63" s="29"/>
       <c r="M63" s="29"/>
       <c r="N63" s="29"/>
@@ -4085,8 +4085,8 @@
       <c r="G64" s="29"/>
       <c r="H64" s="29"/>
       <c r="I64" s="29"/>
-      <c r="J64" s="31"/>
-      <c r="K64" s="32"/>
+      <c r="J64" s="43"/>
+      <c r="K64" s="44"/>
       <c r="L64" s="29"/>
       <c r="M64" s="29"/>
       <c r="N64" s="29"/>
@@ -4118,8 +4118,8 @@
       <c r="G65" s="29"/>
       <c r="H65" s="29"/>
       <c r="I65" s="29"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="32"/>
+      <c r="J65" s="43"/>
+      <c r="K65" s="44"/>
       <c r="L65" s="29"/>
       <c r="M65" s="29"/>
       <c r="N65" s="29"/>
@@ -4151,8 +4151,8 @@
       <c r="G66" s="29"/>
       <c r="H66" s="29"/>
       <c r="I66" s="29"/>
-      <c r="J66" s="31"/>
-      <c r="K66" s="32"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="44"/>
       <c r="L66" s="29"/>
       <c r="M66" s="29"/>
       <c r="N66" s="29"/>
@@ -4184,8 +4184,8 @@
       <c r="G67" s="29"/>
       <c r="H67" s="29"/>
       <c r="I67" s="29"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="32"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="44"/>
       <c r="L67" s="29"/>
       <c r="M67" s="29"/>
       <c r="N67" s="29"/>
@@ -4217,8 +4217,8 @@
       <c r="G68" s="29"/>
       <c r="H68" s="29"/>
       <c r="I68" s="29"/>
-      <c r="J68" s="31"/>
-      <c r="K68" s="32"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="44"/>
       <c r="L68" s="29"/>
       <c r="M68" s="29"/>
       <c r="N68" s="29"/>
@@ -4250,8 +4250,8 @@
       <c r="G69" s="29"/>
       <c r="H69" s="29"/>
       <c r="I69" s="29"/>
-      <c r="J69" s="31"/>
-      <c r="K69" s="32"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="44"/>
       <c r="L69" s="29"/>
       <c r="M69" s="29"/>
       <c r="N69" s="29"/>
@@ -4283,8 +4283,8 @@
       <c r="G70" s="29"/>
       <c r="H70" s="29"/>
       <c r="I70" s="29"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="32"/>
+      <c r="J70" s="43"/>
+      <c r="K70" s="44"/>
       <c r="L70" s="29"/>
       <c r="M70" s="29"/>
       <c r="N70" s="29"/>
@@ -4316,8 +4316,8 @@
       <c r="G71" s="29"/>
       <c r="H71" s="29"/>
       <c r="I71" s="29"/>
-      <c r="J71" s="31"/>
-      <c r="K71" s="32"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="44"/>
       <c r="L71" s="29"/>
       <c r="M71" s="29"/>
       <c r="N71" s="29"/>
@@ -4349,8 +4349,8 @@
       <c r="G72" s="29"/>
       <c r="H72" s="29"/>
       <c r="I72" s="29"/>
-      <c r="J72" s="31"/>
-      <c r="K72" s="32"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="44"/>
       <c r="L72" s="29"/>
       <c r="M72" s="29"/>
       <c r="N72" s="29"/>
@@ -4382,8 +4382,8 @@
       <c r="G73" s="29"/>
       <c r="H73" s="29"/>
       <c r="I73" s="29"/>
-      <c r="J73" s="31"/>
-      <c r="K73" s="32"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="44"/>
       <c r="L73" s="29"/>
       <c r="M73" s="29"/>
       <c r="N73" s="29"/>
@@ -4415,8 +4415,8 @@
       <c r="G74" s="29"/>
       <c r="H74" s="29"/>
       <c r="I74" s="29"/>
-      <c r="J74" s="31"/>
-      <c r="K74" s="32"/>
+      <c r="J74" s="43"/>
+      <c r="K74" s="44"/>
       <c r="L74" s="29"/>
       <c r="M74" s="29"/>
       <c r="N74" s="29"/>
@@ -4448,8 +4448,8 @@
       <c r="G75" s="29"/>
       <c r="H75" s="29"/>
       <c r="I75" s="29"/>
-      <c r="J75" s="31"/>
-      <c r="K75" s="32"/>
+      <c r="J75" s="43"/>
+      <c r="K75" s="44"/>
       <c r="L75" s="29"/>
       <c r="M75" s="29"/>
       <c r="N75" s="29"/>
@@ -4481,8 +4481,8 @@
       <c r="G76" s="29"/>
       <c r="H76" s="29"/>
       <c r="I76" s="29"/>
-      <c r="J76" s="31"/>
-      <c r="K76" s="32"/>
+      <c r="J76" s="43"/>
+      <c r="K76" s="44"/>
       <c r="L76" s="29"/>
       <c r="M76" s="29"/>
       <c r="N76" s="29"/>
@@ -4514,8 +4514,8 @@
       <c r="G77" s="29"/>
       <c r="H77" s="29"/>
       <c r="I77" s="29"/>
-      <c r="J77" s="31"/>
-      <c r="K77" s="32"/>
+      <c r="J77" s="43"/>
+      <c r="K77" s="44"/>
       <c r="L77" s="29"/>
       <c r="M77" s="29"/>
       <c r="N77" s="29"/>
@@ -4547,8 +4547,8 @@
       <c r="G78" s="29"/>
       <c r="H78" s="29"/>
       <c r="I78" s="29"/>
-      <c r="J78" s="31"/>
-      <c r="K78" s="32"/>
+      <c r="J78" s="43"/>
+      <c r="K78" s="44"/>
       <c r="L78" s="29"/>
       <c r="M78" s="29"/>
       <c r="N78" s="29"/>
@@ -4580,8 +4580,8 @@
       <c r="G79" s="29"/>
       <c r="H79" s="29"/>
       <c r="I79" s="29"/>
-      <c r="J79" s="31"/>
-      <c r="K79" s="32"/>
+      <c r="J79" s="43"/>
+      <c r="K79" s="44"/>
       <c r="L79" s="29"/>
       <c r="M79" s="29"/>
       <c r="N79" s="29"/>
@@ -4613,8 +4613,8 @@
       <c r="G80" s="29"/>
       <c r="H80" s="29"/>
       <c r="I80" s="29"/>
-      <c r="J80" s="31"/>
-      <c r="K80" s="32"/>
+      <c r="J80" s="43"/>
+      <c r="K80" s="44"/>
       <c r="L80" s="29"/>
       <c r="M80" s="29"/>
       <c r="N80" s="29"/>
@@ -4646,8 +4646,8 @@
       <c r="G81" s="29"/>
       <c r="H81" s="29"/>
       <c r="I81" s="29"/>
-      <c r="J81" s="31"/>
-      <c r="K81" s="32"/>
+      <c r="J81" s="43"/>
+      <c r="K81" s="44"/>
       <c r="L81" s="29"/>
       <c r="M81" s="29"/>
       <c r="N81" s="29"/>
@@ -4679,8 +4679,8 @@
       <c r="G82" s="29"/>
       <c r="H82" s="29"/>
       <c r="I82" s="29"/>
-      <c r="J82" s="31"/>
-      <c r="K82" s="32"/>
+      <c r="J82" s="43"/>
+      <c r="K82" s="44"/>
       <c r="L82" s="29"/>
       <c r="M82" s="29"/>
       <c r="N82" s="29"/>
@@ -4712,8 +4712,8 @@
       <c r="G83" s="29"/>
       <c r="H83" s="29"/>
       <c r="I83" s="29"/>
-      <c r="J83" s="31"/>
-      <c r="K83" s="32"/>
+      <c r="J83" s="43"/>
+      <c r="K83" s="44"/>
       <c r="L83" s="29"/>
       <c r="M83" s="29"/>
       <c r="N83" s="29"/>
@@ -4745,8 +4745,8 @@
       <c r="G84" s="29"/>
       <c r="H84" s="29"/>
       <c r="I84" s="29"/>
-      <c r="J84" s="31"/>
-      <c r="K84" s="32"/>
+      <c r="J84" s="43"/>
+      <c r="K84" s="44"/>
       <c r="L84" s="29"/>
       <c r="M84" s="29"/>
       <c r="N84" s="29"/>
@@ -4778,8 +4778,8 @@
       <c r="G85" s="29"/>
       <c r="H85" s="29"/>
       <c r="I85" s="29"/>
-      <c r="J85" s="31"/>
-      <c r="K85" s="32"/>
+      <c r="J85" s="43"/>
+      <c r="K85" s="44"/>
       <c r="L85" s="29"/>
       <c r="M85" s="29"/>
       <c r="N85" s="29"/>
@@ -4811,8 +4811,8 @@
       <c r="G86" s="29"/>
       <c r="H86" s="29"/>
       <c r="I86" s="29"/>
-      <c r="J86" s="31"/>
-      <c r="K86" s="32"/>
+      <c r="J86" s="43"/>
+      <c r="K86" s="44"/>
       <c r="L86" s="29"/>
       <c r="M86" s="29"/>
       <c r="N86" s="29"/>
@@ -4844,8 +4844,8 @@
       <c r="G87" s="29"/>
       <c r="H87" s="29"/>
       <c r="I87" s="29"/>
-      <c r="J87" s="31"/>
-      <c r="K87" s="32"/>
+      <c r="J87" s="43"/>
+      <c r="K87" s="44"/>
       <c r="L87" s="29"/>
       <c r="M87" s="29"/>
       <c r="N87" s="29"/>
@@ -4877,8 +4877,8 @@
       <c r="G88" s="29"/>
       <c r="H88" s="29"/>
       <c r="I88" s="29"/>
-      <c r="J88" s="31"/>
-      <c r="K88" s="32"/>
+      <c r="J88" s="43"/>
+      <c r="K88" s="44"/>
       <c r="L88" s="29"/>
       <c r="M88" s="29"/>
       <c r="N88" s="29"/>
@@ -4910,8 +4910,8 @@
       <c r="G89" s="29"/>
       <c r="H89" s="29"/>
       <c r="I89" s="29"/>
-      <c r="J89" s="31"/>
-      <c r="K89" s="32"/>
+      <c r="J89" s="43"/>
+      <c r="K89" s="44"/>
       <c r="L89" s="29"/>
       <c r="M89" s="29"/>
       <c r="N89" s="29"/>
@@ -4943,8 +4943,8 @@
       <c r="G90" s="29"/>
       <c r="H90" s="29"/>
       <c r="I90" s="29"/>
-      <c r="J90" s="31"/>
-      <c r="K90" s="32"/>
+      <c r="J90" s="43"/>
+      <c r="K90" s="44"/>
       <c r="L90" s="29"/>
       <c r="M90" s="29"/>
       <c r="N90" s="29"/>
@@ -4976,8 +4976,8 @@
       <c r="G91" s="29"/>
       <c r="H91" s="29"/>
       <c r="I91" s="29"/>
-      <c r="J91" s="31"/>
-      <c r="K91" s="32"/>
+      <c r="J91" s="43"/>
+      <c r="K91" s="44"/>
       <c r="L91" s="29"/>
       <c r="M91" s="29"/>
       <c r="N91" s="29"/>
@@ -5009,8 +5009,8 @@
       <c r="G92" s="29"/>
       <c r="H92" s="29"/>
       <c r="I92" s="29"/>
-      <c r="J92" s="31"/>
-      <c r="K92" s="32"/>
+      <c r="J92" s="43"/>
+      <c r="K92" s="44"/>
       <c r="L92" s="29"/>
       <c r="M92" s="29"/>
       <c r="N92" s="29"/>
@@ -5042,8 +5042,8 @@
       <c r="G93" s="29"/>
       <c r="H93" s="29"/>
       <c r="I93" s="29"/>
-      <c r="J93" s="31"/>
-      <c r="K93" s="32"/>
+      <c r="J93" s="43"/>
+      <c r="K93" s="44"/>
       <c r="L93" s="29"/>
       <c r="M93" s="29"/>
       <c r="N93" s="29"/>
@@ -5075,8 +5075,8 @@
       <c r="G94" s="29"/>
       <c r="H94" s="29"/>
       <c r="I94" s="29"/>
-      <c r="J94" s="31"/>
-      <c r="K94" s="32"/>
+      <c r="J94" s="43"/>
+      <c r="K94" s="44"/>
       <c r="L94" s="29"/>
       <c r="M94" s="29"/>
       <c r="N94" s="29"/>
@@ -5108,8 +5108,8 @@
       <c r="G95" s="29"/>
       <c r="H95" s="29"/>
       <c r="I95" s="29"/>
-      <c r="J95" s="31"/>
-      <c r="K95" s="32"/>
+      <c r="J95" s="43"/>
+      <c r="K95" s="44"/>
       <c r="L95" s="29"/>
       <c r="M95" s="29"/>
       <c r="N95" s="29"/>
@@ -5141,8 +5141,8 @@
       <c r="G96" s="29"/>
       <c r="H96" s="29"/>
       <c r="I96" s="29"/>
-      <c r="J96" s="31"/>
-      <c r="K96" s="32"/>
+      <c r="J96" s="43"/>
+      <c r="K96" s="44"/>
       <c r="L96" s="29"/>
       <c r="M96" s="29"/>
       <c r="N96" s="29"/>
@@ -5174,8 +5174,8 @@
       <c r="G97" s="29"/>
       <c r="H97" s="29"/>
       <c r="I97" s="29"/>
-      <c r="J97" s="31"/>
-      <c r="K97" s="32"/>
+      <c r="J97" s="43"/>
+      <c r="K97" s="44"/>
       <c r="L97" s="29"/>
       <c r="M97" s="29"/>
       <c r="N97" s="29"/>
@@ -5207,8 +5207,8 @@
       <c r="G98" s="29"/>
       <c r="H98" s="29"/>
       <c r="I98" s="29"/>
-      <c r="J98" s="31"/>
-      <c r="K98" s="32"/>
+      <c r="J98" s="43"/>
+      <c r="K98" s="44"/>
       <c r="L98" s="29"/>
       <c r="M98" s="29"/>
       <c r="N98" s="29"/>
@@ -5240,8 +5240,8 @@
       <c r="G99" s="29"/>
       <c r="H99" s="29"/>
       <c r="I99" s="29"/>
-      <c r="J99" s="31"/>
-      <c r="K99" s="32"/>
+      <c r="J99" s="43"/>
+      <c r="K99" s="44"/>
       <c r="L99" s="29"/>
       <c r="M99" s="29"/>
       <c r="N99" s="29"/>
@@ -5273,8 +5273,8 @@
       <c r="G100" s="29"/>
       <c r="H100" s="29"/>
       <c r="I100" s="29"/>
-      <c r="J100" s="31"/>
-      <c r="K100" s="32"/>
+      <c r="J100" s="43"/>
+      <c r="K100" s="44"/>
       <c r="L100" s="29"/>
       <c r="M100" s="29"/>
       <c r="N100" s="29"/>
@@ -10006,6 +10006,131 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="149">
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="J95:K95"/>
+    <mergeCell ref="J96:K96"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="J91:K91"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="J93:K93"/>
+    <mergeCell ref="J94:K94"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="J82:K82"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="J71:K71"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="J64:K64"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="S4:S6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="T15:T17"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="T18:T20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="S18:S20"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="C15:C17"/>
     <mergeCell ref="S21:S23"/>
     <mergeCell ref="T21:T23"/>
     <mergeCell ref="J3:K3"/>
@@ -10030,131 +10155,6 @@
     <mergeCell ref="S9:S11"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="S4:S6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="T15:T17"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="T18:T20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="S18:S20"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="J65:K65"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="J69:K69"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="J64:K64"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="J70:K70"/>
-    <mergeCell ref="J71:K71"/>
-    <mergeCell ref="J72:K72"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="J82:K82"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J84:K84"/>
-    <mergeCell ref="J100:K100"/>
-    <mergeCell ref="J95:K95"/>
-    <mergeCell ref="J96:K96"/>
-    <mergeCell ref="J97:K97"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="J90:K90"/>
-    <mergeCell ref="J91:K91"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="J93:K93"/>
-    <mergeCell ref="J94:K94"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="O4:O200 M4:M200 K9:K24 K101:K200" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -10187,10 +10187,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C1" s="3"/>
     </row>
@@ -10199,48 +10199,48 @@
         <v>2</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C2" s="38"/>
     </row>
     <row r="3" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10248,7 +10248,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10256,7 +10256,7 @@
         <v>19</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10264,7 +10264,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10272,7 +10272,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10280,7 +10280,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10288,7 +10288,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
